--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261019.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261019.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>3,513,000</t>
+          <t>2,360,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,360,000</t>
+          <t>9,663,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>9,663,000</t>
+          <t>3,513,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>21,718,000</t>
+          <t>5,379,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>5,379,000</t>
+          <t>21,718,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
